--- a/voice_lines.xlsx
+++ b/voice_lines.xlsx
@@ -2,7 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="VoiceLines" sheetId="1" r:id="rId1"/>
+    <sheet name="캐릭터" sheetId="1" r:id="rId1"/>
+    <sheet name="대사목록" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -71,11 +72,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="46" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="6" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -86,27 +86,22 @@
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">카테고리</t>
+          <t xml:space="preserve">이름</t>
         </is>
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">캐릭터</t>
+          <t xml:space="preserve">성별</t>
         </is>
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">대사</t>
+          <t xml:space="preserve">키(파일명)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">mp3 파일명 (voice 폴더)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">비고</t>
+          <t xml:space="preserve">역할/비고</t>
         </is>
       </c>
     </row>
@@ -116,27 +111,22 @@
       </c>
       <c r="B2" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">남</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">출발 신호 떨어졌습니다! 레이스 스타트!</t>
+          <t xml:space="preserve">minho</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">cast_start_1.mp3</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">밸런스/라이벌·플레이어(LA BOMBA)</t>
         </is>
       </c>
     </row>
@@ -146,27 +136,22 @@
       </c>
       <c r="B3" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계</t>
+          <t xml:space="preserve">박지성</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">남</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">자 드디어 출발합니다!</t>
+          <t xml:space="preserve">jisung</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">cast_start_2.mp3</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">머슬카/라이벌·플레이어(THUNDER)</t>
         </is>
       </c>
     </row>
@@ -176,27 +161,22 @@
       </c>
       <c r="B4" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계</t>
+          <t xml:space="preserve">이준</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">남</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">그린 라이트, 일제히 튀어나갑니다!</t>
+          <t xml:space="preserve">jun</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">cast_start_3.mp3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">라이벌</t>
         </is>
       </c>
     </row>
@@ -206,27 +186,22 @@
       </c>
       <c r="B5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계</t>
+          <t xml:space="preserve">한소희</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">여</t>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">추월합니다! 순위를 끌어올립니다!</t>
+          <t xml:space="preserve">sohee</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">cast_overtake_1.mp3</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">슈퍼카/라이벌·플레이어(VIPER)</t>
         </is>
       </c>
     </row>
@@ -236,27 +211,22 @@
       </c>
       <c r="B6" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계</t>
+          <t xml:space="preserve">김유나</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">여</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">앞차를 제칩니다! 멋진 추월!</t>
+          <t xml:space="preserve">yuna</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">cast_overtake_2.mp3</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">라이벌</t>
         </is>
       </c>
     </row>
@@ -266,27 +236,22 @@
       </c>
       <c r="B7" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계</t>
+          <t xml:space="preserve">정태양</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">남</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">파고듭니다, 한 계단 올라섭니다!</t>
+          <t xml:space="preserve">taeyang</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">cast_overtake_3.mp3</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SUV/라이벌·플레이어(BULL)</t>
         </is>
       </c>
     </row>
@@ -296,27 +261,22 @@
       </c>
       <c r="B8" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계</t>
+          <t xml:space="preserve">서아린</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">여</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">아, 따라잡힙니다! 순위를 내줍니다.</t>
+          <t xml:space="preserve">arin</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">cast_passed_1.mp3</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">라이벌</t>
         </is>
       </c>
     </row>
@@ -326,25 +286,355 @@
       </c>
       <c r="B9" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">bora</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">라이벌</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="6" customWidth="1"/>
+    <col min="5" max="5" width="46" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">번호</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">카테고리</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">캐릭터</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">성별</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">mp3 파일명 (voice 폴더)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">중계</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">중계</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">출발 신호 떨어졌습니다! 레이스 스타트!</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">cast_start_1.mp3</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">중계</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">중계</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">자 드디어 출발합니다!</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">cast_start_2.mp3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">중계</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">중계</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">그린 라이트, 일제히 튀어나갑니다!</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">cast_start_3.mp3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">중계</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">중계</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">추월합니다! 순위를 끌어올립니다!</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">cast_overtake_1.mp3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">중계</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">중계</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">앞차를 제칩니다! 멋진 추월!</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">cast_overtake_2.mp3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">중계</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">중계</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">파고듭니다, 한 계단 올라섭니다!</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">cast_overtake_3.mp3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">중계</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">중계</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아, 따라잡힙니다! 순위를 내줍니다.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">cast_passed_1.mp3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">중계</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">중계</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">앞으로 치고 나가는 라이벌, 자리를 빼앗깁니다.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr" s="3">
+      <c r="F9" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">cast_passed_2.mp3</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr" s="3">
+      <c r="G9" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -361,20 +651,25 @@
       </c>
       <c r="C10" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">중계</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">밀립니다! 한 계단 내려갑니다.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr" s="3">
+      <c r="F10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">cast_passed_3.mp3</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr" s="3">
+      <c r="G10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -391,20 +686,25 @@
       </c>
       <c r="C11" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">중계</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">선두로 올라섭니다! 1위입니다!</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr" s="3">
+      <c r="F11" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">cast_lead_1.mp3</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr" s="3">
+      <c r="G11" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -421,20 +721,25 @@
       </c>
       <c r="C12" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">중계</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">마침내 선두 자리를 차지합니다!</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr" s="3">
+      <c r="F12" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">cast_lead_2.mp3</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr" s="3">
+      <c r="G12" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -451,20 +756,25 @@
       </c>
       <c r="C13" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">중계</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">1위 등극! 이대로 질주합니다!</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr" s="3">
+      <c r="F13" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">cast_lead_3.mp3</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr" s="3">
+      <c r="G13" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -481,20 +791,25 @@
       </c>
       <c r="C14" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">중계</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">아! 충돌입니다! 속도가 확 줄었습니다.</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr" s="3">
+      <c r="F14" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">cast_crash_1.mp3</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr" s="3">
+      <c r="G14" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -511,20 +826,25 @@
       </c>
       <c r="C15" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">중계</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">부딪혔어요! 페이스가 흐트러집니다.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr" s="3">
+      <c r="F15" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">cast_crash_2.mp3</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr" s="3">
+      <c r="G15" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -541,20 +861,25 @@
       </c>
       <c r="C16" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">중계</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">추돌! 위험합니다, 다시 가속해야 합니다.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr" s="3">
+      <c r="F16" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">cast_crash_3.mp3</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr" s="3">
+      <c r="G16" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -571,20 +896,25 @@
       </c>
       <c r="C17" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">중계</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">체크포인트 통과! 시간 추가됐습니다.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr" s="3">
+      <c r="F17" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">cast_checkpoint_1.mp3</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr" s="3">
+      <c r="G17" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -601,20 +931,25 @@
       </c>
       <c r="C18" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">중계</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">관문 통과, 시간을 벌었습니다!</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr" s="3">
+      <c r="F18" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">cast_checkpoint_2.mp3</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr" s="3">
+      <c r="G18" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -631,20 +966,25 @@
       </c>
       <c r="C19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">중계</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">체크포인트 클리어! 계속 달립니다.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr" s="3">
+      <c r="F19" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">cast_checkpoint_3.mp3</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr" s="3">
+      <c r="G19" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -661,20 +1001,25 @@
       </c>
       <c r="C20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">중계</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">시간이 얼마 없습니다! 서둘러야 해요!</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr" s="3">
+      <c r="F20" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">cast_timelow_1.mp3</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr" s="3">
+      <c r="G20" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -691,20 +1036,25 @@
       </c>
       <c r="C21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">중계</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">이런, 시간 부족합니다! 풀스로틀!</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr" s="3">
+      <c r="F21" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">cast_timelow_2.mp3</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr" s="3">
+      <c r="G21" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -721,20 +1071,25 @@
       </c>
       <c r="C22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">중계(여성)</t>
+          <t xml:space="preserve">중계</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">초읽기 들어갑니다, 더 밟아야 합니다!</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr" s="3">
+      <c r="F22" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">cast_timelow_3.mp3</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr" s="3">
+      <c r="G22" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -751,20 +1106,25 @@
       </c>
       <c r="C23" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">덤벼봐!</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_taunt_1.mp3</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_taunt_1.mp3</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">도발</t>
         </is>
@@ -781,20 +1141,25 @@
       </c>
       <c r="C24" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">느려!</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_taunt_2.mp3</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_taunt_2.mp3</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">도발</t>
         </is>
@@ -811,20 +1176,25 @@
       </c>
       <c r="C25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">내가 우승하겠어!</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_taunt_3.mp3</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_taunt_3.mp3</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">도발</t>
         </is>
@@ -841,20 +1211,25 @@
       </c>
       <c r="C26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">이 정도냐!</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_taunt_4.mp3</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_taunt_4.mp3</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">도발</t>
         </is>
@@ -871,20 +1246,25 @@
       </c>
       <c r="C27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">따라와 봐!</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_taunt_5.mp3</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_taunt_5.mp3</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">도발</t>
         </is>
@@ -901,20 +1281,25 @@
       </c>
       <c r="C28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">신나는데!</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_happy_1.mp3</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_happy_1.mp3</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">기쁨</t>
         </is>
@@ -931,20 +1316,25 @@
       </c>
       <c r="C29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">좋았어!</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_happy_2.mp3</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_happy_2.mp3</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">기쁨</t>
         </is>
@@ -961,20 +1351,25 @@
       </c>
       <c r="C30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">이거 재밌군!</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_happy_3.mp3</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_happy_3.mp3</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">기쁨</t>
         </is>
@@ -991,20 +1386,25 @@
       </c>
       <c r="C31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">가속 끝내주는데!</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_happy_4.mp3</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_happy_4.mp3</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">기쁨</t>
         </is>
@@ -1021,22 +1421,27 @@
       </c>
       <c r="C32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">으악!</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_shock_1.mp3</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">놀람(shock·itemHit 공용)</t>
+          <t xml:space="preserve">line_minho_shock_1.mp3</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람(아이템피격 '으악!' 공용)</t>
         </is>
       </c>
     </row>
@@ -1051,20 +1456,25 @@
       </c>
       <c r="C33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">위험해!</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_shock_2.mp3</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_shock_2.mp3</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">놀람</t>
         </is>
@@ -1081,20 +1491,25 @@
       </c>
       <c r="C34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">피해!</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_shock_3.mp3</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_shock_3.mp3</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">놀람</t>
         </is>
@@ -1111,20 +1526,25 @@
       </c>
       <c r="C35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">안 돼!</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_shock_4.mp3</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_shock_4.mp3</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">놀람</t>
         </is>
@@ -1141,20 +1561,25 @@
       </c>
       <c r="C36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">누가 여기다 이런 걸 둔 거야?</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_itemhit_2.mp3</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_itemhit_2.mp3</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">아이템 피격</t>
         </is>
@@ -1171,20 +1596,25 @@
       </c>
       <c r="C37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">이런!</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_itemhit_3.mp3</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_itemhit_3.mp3</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">아이템 피격</t>
         </is>
@@ -1201,20 +1631,25 @@
       </c>
       <c r="C38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">말도 안 돼!</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_itemhit_4.mp3</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_itemhit_4.mp3</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">아이템 피격</t>
         </is>
@@ -1231,20 +1666,25 @@
       </c>
       <c r="C39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">미사일이다!</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_missileseen_1.mp3</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_missileseen_1.mp3</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">미사일 발견</t>
         </is>
@@ -1261,20 +1701,25 @@
       </c>
       <c r="C40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">피해야 해!</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_missileseen_2.mp3</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_missileseen_2.mp3</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">미사일 발견</t>
         </is>
@@ -1291,20 +1736,25 @@
       </c>
       <c r="C41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">날아온다!</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_missileseen_3.mp3</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_missileseen_3.mp3</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">미사일 발견</t>
         </is>
@@ -1321,20 +1771,25 @@
       </c>
       <c r="C42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">두고 보자!</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_angry_1.mp3</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_angry_1.mp3</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">분노</t>
         </is>
@@ -1351,20 +1806,25 @@
       </c>
       <c r="C43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">반칙이야!</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_angry_2.mp3</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_angry_2.mp3</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">분노</t>
         </is>
@@ -1381,20 +1841,25 @@
       </c>
       <c r="C44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">라이벌/플레이어 공용</t>
+          <t xml:space="preserve">강민호</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">이대론 못 끝내!</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">line_angry_3.mp3</t>
-        </is>
-      </c>
       <c r="F44" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_minho_angry_3.mp3</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">분노</t>
         </is>
@@ -1406,27 +1871,32 @@
       </c>
       <c r="B45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">군중</t>
+          <t xml:space="preserve">대사</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">길가 사람들</t>
+          <t xml:space="preserve">박지성</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">와! 배트맨이다!</t>
+          <t xml:space="preserve">남</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">crowd_1.mp3</t>
+          <t xml:space="preserve">덤벼봐!</t>
         </is>
       </c>
       <c r="F45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">배트맨 등장</t>
+          <t xml:space="preserve">line_jisung_taunt_1.mp3</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
         </is>
       </c>
     </row>
@@ -1436,27 +1906,32 @@
       </c>
       <c r="B46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">군중</t>
+          <t xml:space="preserve">대사</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">길가 사람들</t>
+          <t xml:space="preserve">박지성</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">와! 스파이더맨이다!</t>
+          <t xml:space="preserve">남</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">crowd_2.mp3</t>
+          <t xml:space="preserve">느려!</t>
         </is>
       </c>
       <c r="F46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">스파이더맨 등장</t>
+          <t xml:space="preserve">line_jisung_taunt_2.mp3</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
         </is>
       </c>
     </row>
@@ -1466,27 +1941,32 @@
       </c>
       <c r="B47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">군중</t>
+          <t xml:space="preserve">대사</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">길가 사람들</t>
+          <t xml:space="preserve">박지성</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">우와, 슈퍼맨이다!</t>
+          <t xml:space="preserve">남</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">crowd_3.mp3</t>
+          <t xml:space="preserve">내가 우승하겠어!</t>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">슈퍼맨 등장</t>
+          <t xml:space="preserve">line_jisung_taunt_3.mp3</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
         </is>
       </c>
     </row>
@@ -1496,27 +1976,32 @@
       </c>
       <c r="B48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">군중</t>
+          <t xml:space="preserve">대사</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">길가 사람들</t>
+          <t xml:space="preserve">박지성</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">저기 봐, UFO다!</t>
+          <t xml:space="preserve">남</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">crowd_4.mp3</t>
+          <t xml:space="preserve">이 정도냐!</t>
         </is>
       </c>
       <c r="F48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">UFO 등장</t>
+          <t xml:space="preserve">line_jisung_taunt_4.mp3</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
         </is>
       </c>
     </row>
@@ -1526,27 +2011,32 @@
       </c>
       <c r="B49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">군중</t>
+          <t xml:space="preserve">대사</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">길가 사람들</t>
+          <t xml:space="preserve">박지성</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">조커잖아, 도망쳐!</t>
+          <t xml:space="preserve">남</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">crowd_5.mp3</t>
+          <t xml:space="preserve">따라와 봐!</t>
         </is>
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">UFO 등장</t>
+          <t xml:space="preserve">line_jisung_taunt_5.mp3</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
         </is>
       </c>
     </row>
@@ -1556,31 +2046,5426 @@
       </c>
       <c r="B50" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">박지성</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">신나는데!</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jisung_happy_1.mp3</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">박지성</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">좋았어!</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jisung_happy_2.mp3</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">박지성</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이거 재밌군!</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jisung_happy_3.mp3</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">박지성</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">가속 끝내주는데!</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jisung_happy_4.mp3</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">박지성</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">으악!</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jisung_shock_1.mp3</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람(아이템피격 '으악!' 공용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">박지성</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">위험해!</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jisung_shock_2.mp3</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">박지성</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">피해!</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jisung_shock_3.mp3</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">박지성</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">안 돼!</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jisung_shock_4.mp3</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">박지성</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">누가 여기다 이런 걸 둔 거야?</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jisung_itemhit_2.mp3</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">박지성</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이런!</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jisung_itemhit_3.mp3</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">박지성</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">말도 안 돼!</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jisung_itemhit_4.mp3</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">박지성</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일이다!</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jisung_missileseen_1.mp3</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">박지성</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">피해야 해!</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jisung_missileseen_2.mp3</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">박지성</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">날아온다!</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jisung_missileseen_3.mp3</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">박지성</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">두고 보자!</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jisung_angry_1.mp3</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">박지성</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">반칙이야!</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jisung_angry_2.mp3</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">박지성</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이대론 못 끝내!</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jisung_angry_3.mp3</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">덤벼봐!</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_taunt_1.mp3</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">느려!</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_taunt_2.mp3</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">내가 우승하겠어!</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_taunt_3.mp3</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이 정도냐!</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_taunt_4.mp3</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">따라와 봐!</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_taunt_5.mp3</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">신나는데!</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_happy_1.mp3</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">좋았어!</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_happy_2.mp3</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이거 재밌군!</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_happy_3.mp3</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">가속 끝내주는데!</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_happy_4.mp3</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">으악!</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_shock_1.mp3</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람(아이템피격 '으악!' 공용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">위험해!</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_shock_2.mp3</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">피해!</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_shock_3.mp3</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">안 돼!</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_shock_4.mp3</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">누가 여기다 이런 걸 둔 거야?</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_itemhit_2.mp3</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이런!</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_itemhit_3.mp3</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">말도 안 돼!</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_itemhit_4.mp3</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일이다!</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_missileseen_1.mp3</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">피해야 해!</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_missileseen_2.mp3</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">날아온다!</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_missileseen_3.mp3</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">두고 보자!</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_angry_1.mp3</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">반칙이야!</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_angry_2.mp3</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이준</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이대론 못 끝내!</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_jun_angry_3.mp3</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">덤벼봐!</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_taunt_1.mp3</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">느려!</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_taunt_2.mp3</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">내가 우승하겠어!</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_taunt_3.mp3</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이 정도냐!</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_taunt_4.mp3</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">따라와 봐!</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_taunt_5.mp3</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">신나는데!</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_happy_1.mp3</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">좋았어!</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_happy_2.mp3</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이거 재밌군!</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_happy_3.mp3</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">가속 끝내주는데!</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_happy_4.mp3</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">으악!</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_shock_1.mp3</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람(아이템피격 '으악!' 공용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">위험해!</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_shock_2.mp3</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">피해!</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_shock_3.mp3</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">안 돼!</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_shock_4.mp3</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">누가 여기다 이런 걸 둔 거야?</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_itemhit_2.mp3</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이런!</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_itemhit_3.mp3</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">말도 안 돼!</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_itemhit_4.mp3</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일이다!</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_missileseen_1.mp3</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">피해야 해!</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_missileseen_2.mp3</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">날아온다!</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_missileseen_3.mp3</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">두고 보자!</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_angry_1.mp3</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">반칙이야!</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_angry_2.mp3</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">한소희</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이대론 못 끝내!</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_sohee_angry_3.mp3</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">덤벼봐!</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_taunt_1.mp3</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">느려!</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_taunt_2.mp3</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">내가 우승하겠어!</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_taunt_3.mp3</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이 정도냐!</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_taunt_4.mp3</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">따라와 봐!</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_taunt_5.mp3</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">신나는데!</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_happy_1.mp3</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">좋았어!</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_happy_2.mp3</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이거 재밌군!</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_happy_3.mp3</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">가속 끝내주는데!</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_happy_4.mp3</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">으악!</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_shock_1.mp3</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람(아이템피격 '으악!' 공용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">위험해!</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_shock_2.mp3</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">피해!</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_shock_3.mp3</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">안 돼!</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_shock_4.mp3</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">누가 여기다 이런 걸 둔 거야?</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_itemhit_2.mp3</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이런!</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_itemhit_3.mp3</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">말도 안 돼!</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_itemhit_4.mp3</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일이다!</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_missileseen_1.mp3</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">피해야 해!</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_missileseen_2.mp3</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">날아온다!</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_missileseen_3.mp3</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">두고 보자!</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_angry_1.mp3</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">반칙이야!</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_angry_2.mp3</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">김유나</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이대론 못 끝내!</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_yuna_angry_3.mp3</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">덤벼봐!</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_taunt_1.mp3</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">느려!</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_taunt_2.mp3</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">내가 우승하겠어!</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_taunt_3.mp3</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이 정도냐!</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_taunt_4.mp3</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">따라와 봐!</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_taunt_5.mp3</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">신나는데!</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_happy_1.mp3</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">좋았어!</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_happy_2.mp3</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이거 재밌군!</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_happy_3.mp3</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">가속 끝내주는데!</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_happy_4.mp3</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">으악!</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_shock_1.mp3</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람(아이템피격 '으악!' 공용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">위험해!</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_shock_2.mp3</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">피해!</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_shock_3.mp3</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">안 돼!</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_shock_4.mp3</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">누가 여기다 이런 걸 둔 거야?</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_itemhit_2.mp3</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이런!</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_itemhit_3.mp3</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">말도 안 돼!</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_itemhit_4.mp3</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일이다!</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_missileseen_1.mp3</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">피해야 해!</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_missileseen_2.mp3</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">날아온다!</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_missileseen_3.mp3</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">두고 보자!</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_angry_1.mp3</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">반칙이야!</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_angry_2.mp3</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">정태양</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이대론 못 끝내!</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_taeyang_angry_3.mp3</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">덤벼봐!</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_taunt_1.mp3</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">느려!</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_taunt_2.mp3</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">내가 우승하겠어!</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_taunt_3.mp3</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이 정도냐!</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_taunt_4.mp3</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">따라와 봐!</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_taunt_5.mp3</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">신나는데!</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_happy_1.mp3</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">좋았어!</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_happy_2.mp3</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이거 재밌군!</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_happy_3.mp3</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">가속 끝내주는데!</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_happy_4.mp3</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">으악!</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_shock_1.mp3</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람(아이템피격 '으악!' 공용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">위험해!</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_shock_2.mp3</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">피해!</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_shock_3.mp3</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">안 돼!</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_shock_4.mp3</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">누가 여기다 이런 걸 둔 거야?</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_itemhit_2.mp3</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이런!</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_itemhit_3.mp3</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">말도 안 돼!</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_itemhit_4.mp3</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일이다!</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_missileseen_1.mp3</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">피해야 해!</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_missileseen_2.mp3</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">날아온다!</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_missileseen_3.mp3</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">두고 보자!</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_angry_1.mp3</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">반칙이야!</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_angry_2.mp3</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">서아린</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이대론 못 끝내!</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_arin_angry_3.mp3</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">덤벼봐!</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_taunt_1.mp3</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">느려!</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_taunt_2.mp3</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">내가 우승하겠어!</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_taunt_3.mp3</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이 정도냐!</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_taunt_4.mp3</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">따라와 봐!</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_taunt_5.mp3</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">도발</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">신나는데!</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_happy_1.mp3</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">좋았어!</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_happy_2.mp3</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이거 재밌군!</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_happy_3.mp3</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">가속 끝내주는데!</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_happy_4.mp3</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">기쁨</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">으악!</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_shock_1.mp3</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람(아이템피격 '으악!' 공용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">위험해!</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_shock_2.mp3</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">피해!</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_shock_3.mp3</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">안 돼!</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_shock_4.mp3</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">놀람</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">누가 여기다 이런 걸 둔 거야?</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_itemhit_2.mp3</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이런!</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_itemhit_3.mp3</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">말도 안 돼!</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_itemhit_4.mp3</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">아이템 피격</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일이다!</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_missileseen_1.mp3</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">피해야 해!</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_missileseen_2.mp3</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2">
+        <v>194</v>
+      </c>
+      <c r="B195" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">날아온다!</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_missileseen_3.mp3</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">미사일 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2">
+        <v>195</v>
+      </c>
+      <c r="B196" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">두고 보자!</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_angry_1.mp3</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2">
+        <v>196</v>
+      </c>
+      <c r="B197" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">반칙이야!</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_angry_2.mp3</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">대사</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">최보라</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">이대론 못 끝내!</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">line_bora_angry_3.mp3</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">분노</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">군중</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">길가 사람들</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">와! 배트맨이다!</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">crowd_1.mp3</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">배트맨 등장</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">군중</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">길가 사람들</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">와! 스파이더맨이다!</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">crowd_2.mp3</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">스파이더맨 등장</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2">
+        <v>200</v>
+      </c>
+      <c r="B201" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">군중</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">길가 사람들</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">우와, 슈퍼맨이다!</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">crowd_3.mp3</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">슈퍼맨 등장</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2">
+        <v>201</v>
+      </c>
+      <c r="B202" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">군중</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">길가 사람들</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">저기 봐, UFO다!</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">crowd_4.mp3</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">UFO 등장</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2">
+        <v>202</v>
+      </c>
+      <c r="B203" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">군중</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">길가 사람들</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">조커잖아, 도망쳐!</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">crowd_5.mp3</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">UFO 등장</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2">
+        <v>203</v>
+      </c>
+      <c r="B204" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">조커</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">조커(UFO)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr" s="3">
+      <c r="C204" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">조커</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">하하하하! 비켜라!</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr" s="3">
+      <c r="F204" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">joker_1.mp3</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr" s="3">
+      <c r="G204" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">UFO 등장 시</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F50"/>
+  <autoFilter ref="A1:G204"/>
 </worksheet>
 </file>